--- a/documentations/import/tires.xlsx
+++ b/documentations/import/tires.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\perminoviv\my\imsd-ai\backend\documentations\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7232DB96-8ADC-44FA-830E-B599A3FA331C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9739FE-2231-4547-81D0-20B54D7A286A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2318,13 +2318,13 @@
   <dimension ref="A1:AF383"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="18" max="18" width="39.5703125" customWidth="1"/>
+    <col min="18" max="18" width="62.85546875" customWidth="1"/>
     <col min="19" max="19" width="34.5703125" customWidth="1"/>
     <col min="20" max="20" width="29" customWidth="1"/>
     <col min="21" max="21" width="25.85546875" customWidth="1"/>
     <col min="22" max="22" width="47.28515625" customWidth="1"/>
     <col min="23" max="23" width="41.140625" customWidth="1"/>
-    <col min="24" max="24" width="30" customWidth="1"/>
+    <col min="24" max="24" width="77.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
